--- a/申請書/和裕維力貸商品範本.xlsx
+++ b/申請書/和裕維力貸商品範本.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cfe2efa93682d330/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbf32e69ea87f61e/Desktop/claude/申請書/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="28715" documentId="13_ncr:1_{499913D0-2FE9-4655-B8BA-1A17E70F9329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FC2694E-E060-4583-9BC3-E0E432FCCE22}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{99901B22-9634-4B91-9650-179AA17524FA}"/>
+    <workbookView xWindow="9510" yWindow="1995" windowWidth="17340" windowHeight="13485" xr2:uid="{99901B22-9634-4B91-9650-179AA17524FA}"/>
   </bookViews>
   <sheets>
     <sheet name="和裕維力貸" sheetId="7" r:id="rId1"/>
@@ -2112,6 +2112,37 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2120,17 +2151,96 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2141,6 +2251,17 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
@@ -2149,32 +2270,24 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2195,129 +2308,16 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2335,10 +2335,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3219,16 +3215,16 @@
       </c>
     </row>
     <row r="7" spans="2:43" ht="26.25" thickBot="1">
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="83" t="s">
         <v>171</v>
       </c>
-      <c r="C7" s="65"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="65"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
       <c r="K7" s="6"/>
       <c r="R7" s="2" t="s">
         <v>68</v>
@@ -3319,15 +3315,15 @@
       <c r="B8" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="54"/>
-      <c r="D8" s="55"/>
+      <c r="C8" s="84"/>
+      <c r="D8" s="85"/>
       <c r="E8" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="F8" s="54" t="s">
+      <c r="F8" s="84" t="s">
         <v>210</v>
       </c>
-      <c r="G8" s="55"/>
+      <c r="G8" s="85"/>
       <c r="I8" s="41"/>
       <c r="J8" s="8"/>
       <c r="Q8" s="2" t="s">
@@ -3347,10 +3343,10 @@
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
-      <c r="H9" s="56" t="s">
+      <c r="H9" s="75" t="s">
         <v>207</v>
       </c>
-      <c r="I9" s="56"/>
+      <c r="I9" s="75"/>
       <c r="Q9" s="2" t="s">
         <v>205</v>
       </c>
@@ -3362,16 +3358,16 @@
       </c>
     </row>
     <row r="10" spans="2:43">
-      <c r="B10" s="57" t="s">
+      <c r="B10" s="45" t="s">
         <v>110</v>
       </c>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="59"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="47"/>
       <c r="J10" s="10"/>
       <c r="Q10" s="2" t="s">
         <v>206</v>
@@ -3441,19 +3437,19 @@
       <c r="B11" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C11" s="70" t="s">
+      <c r="C11" s="79" t="s">
         <v>212</v>
       </c>
-      <c r="D11" s="71"/>
+      <c r="D11" s="77"/>
       <c r="E11" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="F11" s="71" t="s">
+      <c r="F11" s="77" t="s">
         <v>213</v>
       </c>
-      <c r="G11" s="71"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="61"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="95"/>
       <c r="J11" s="8"/>
       <c r="R11" s="2" t="s">
         <v>72</v>
@@ -3541,21 +3537,21 @@
       <c r="B12" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="52" t="s">
         <v>214</v>
       </c>
-      <c r="D12" s="43"/>
+      <c r="D12" s="53"/>
       <c r="E12" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="F12" s="42" t="s">
+      <c r="F12" s="52" t="s">
         <v>215</v>
       </c>
-      <c r="G12" s="43"/>
-      <c r="H12" s="68" t="s">
+      <c r="G12" s="53"/>
+      <c r="H12" s="90" t="s">
         <v>172</v>
       </c>
-      <c r="I12" s="69"/>
+      <c r="I12" s="91"/>
       <c r="R12" s="2" t="s">
         <v>73</v>
       </c>
@@ -3642,19 +3638,19 @@
       <c r="B13" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="43"/>
+      <c r="D13" s="53"/>
       <c r="E13" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="F13" s="42" t="s">
+      <c r="F13" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="43"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="45"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="92"/>
+      <c r="I13" s="93"/>
       <c r="Q13" s="2" t="s">
         <v>148</v>
       </c>
@@ -3744,21 +3740,21 @@
       <c r="B14" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="C14" s="42" t="s">
+      <c r="C14" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="43"/>
+      <c r="D14" s="53"/>
       <c r="E14" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="F14" s="42" t="s">
+      <c r="F14" s="52" t="s">
         <v>216</v>
       </c>
-      <c r="G14" s="43"/>
-      <c r="H14" s="94" t="s">
+      <c r="G14" s="53"/>
+      <c r="H14" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="I14" s="95"/>
+      <c r="I14" s="59"/>
       <c r="Q14" s="2" t="s">
         <v>149</v>
       </c>
@@ -3848,17 +3844,17 @@
       <c r="B15" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C15" s="48" t="s">
+      <c r="C15" s="81" t="s">
         <v>218</v>
       </c>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="67"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="82"/>
+      <c r="F15" s="89"/>
       <c r="G15" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="H15" s="42"/>
-      <c r="I15" s="47"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="56"/>
       <c r="Q15" s="2" t="s">
         <v>150</v>
       </c>
@@ -3948,19 +3944,19 @@
       <c r="B16" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="C16" s="48" t="s">
+      <c r="C16" s="81" t="s">
         <v>219</v>
       </c>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="67"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="82"/>
+      <c r="F16" s="89"/>
       <c r="G16" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="H16" s="42" t="s">
+      <c r="H16" s="52" t="s">
         <v>123</v>
       </c>
-      <c r="I16" s="47"/>
+      <c r="I16" s="56"/>
       <c r="Q16" s="2" t="s">
         <v>151</v>
       </c>
@@ -4050,10 +4046,10 @@
       <c r="B17" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="C17" s="42" t="s">
+      <c r="C17" s="52" t="s">
         <v>216</v>
       </c>
-      <c r="D17" s="43"/>
+      <c r="D17" s="53"/>
       <c r="E17" s="12" t="s">
         <v>194</v>
       </c>
@@ -4063,10 +4059,10 @@
       <c r="G17" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="H17" s="42" t="s">
+      <c r="H17" s="52" t="s">
         <v>217</v>
       </c>
-      <c r="I17" s="47"/>
+      <c r="I17" s="56"/>
       <c r="Q17" s="2" t="s">
         <v>152</v>
       </c>
@@ -4081,11 +4077,11 @@
       <c r="B18" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="C18" s="50" t="s">
+      <c r="C18" s="86" t="s">
         <v>220</v>
       </c>
-      <c r="D18" s="51"/>
-      <c r="E18" s="66"/>
+      <c r="D18" s="87"/>
+      <c r="E18" s="88"/>
       <c r="F18" s="14" t="s">
         <v>127</v>
       </c>
@@ -4112,11 +4108,11 @@
       <c r="B19" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="C19" s="89" t="s">
+      <c r="C19" s="48" t="s">
         <v>224</v>
       </c>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
       <c r="F19" s="12" t="s">
         <v>130</v>
       </c>
@@ -4143,17 +4139,17 @@
       <c r="B20" s="30" t="s">
         <v>195</v>
       </c>
-      <c r="C20" s="73" t="s">
+      <c r="C20" s="54" t="s">
         <v>225</v>
       </c>
-      <c r="D20" s="74"/>
+      <c r="D20" s="55"/>
       <c r="E20" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="F20" s="62"/>
-      <c r="G20" s="63"/>
-      <c r="H20" s="63"/>
-      <c r="I20" s="64"/>
+      <c r="F20" s="96"/>
+      <c r="G20" s="97"/>
+      <c r="H20" s="97"/>
+      <c r="I20" s="98"/>
       <c r="Q20" s="2" t="s">
         <v>155</v>
       </c>
@@ -4191,17 +4187,17 @@
       </c>
     </row>
     <row r="22" spans="1:43">
-      <c r="B22" s="90" t="s">
+      <c r="B22" s="49" t="s">
         <v>132</v>
       </c>
-      <c r="C22" s="91"/>
+      <c r="C22" s="50"/>
       <c r="D22" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E22" s="92" t="s">
+      <c r="E22" s="51" t="s">
         <v>133</v>
       </c>
-      <c r="F22" s="91"/>
+      <c r="F22" s="50"/>
       <c r="G22" s="4" t="s">
         <v>209</v>
       </c>
@@ -4246,17 +4242,17 @@
       <c r="B23" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="C23" s="42" t="s">
+      <c r="C23" s="52" t="s">
         <v>226</v>
       </c>
-      <c r="D23" s="43"/>
+      <c r="D23" s="53"/>
       <c r="E23" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="F23" s="42" t="s">
+      <c r="F23" s="52" t="s">
         <v>227</v>
       </c>
-      <c r="G23" s="47"/>
+      <c r="G23" s="56"/>
       <c r="Q23" s="2" t="s">
         <v>158</v>
       </c>
@@ -4322,17 +4318,17 @@
       <c r="B24" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="C24" s="42" t="s">
+      <c r="C24" s="52" t="s">
         <v>228</v>
       </c>
-      <c r="D24" s="43"/>
+      <c r="D24" s="53"/>
       <c r="E24" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="F24" s="42" t="s">
+      <c r="F24" s="52" t="s">
         <v>211</v>
       </c>
-      <c r="G24" s="47"/>
+      <c r="G24" s="56"/>
       <c r="Q24" s="2" t="s">
         <v>159</v>
       </c>
@@ -4398,17 +4394,17 @@
       <c r="B25" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="C25" s="73" t="s">
+      <c r="C25" s="54" t="s">
         <v>229</v>
       </c>
-      <c r="D25" s="74"/>
+      <c r="D25" s="55"/>
       <c r="E25" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="F25" s="73" t="s">
+      <c r="F25" s="54" t="s">
         <v>230</v>
       </c>
-      <c r="G25" s="93"/>
+      <c r="G25" s="57"/>
       <c r="H25" s="2" t="s">
         <v>119</v>
       </c>
@@ -4586,19 +4582,19 @@
       </c>
     </row>
     <row r="27" spans="1:43">
-      <c r="A27" s="46" t="s">
+      <c r="A27" s="99" t="s">
         <v>200</v>
       </c>
-      <c r="B27" s="57" t="s">
+      <c r="B27" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="59"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="47"/>
       <c r="Q27" s="2" t="s">
         <v>162</v>
       </c>
@@ -4686,21 +4682,21 @@
       </c>
     </row>
     <row r="28" spans="1:43">
-      <c r="A28" s="46"/>
+      <c r="A28" s="99"/>
       <c r="B28" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C28" s="42"/>
-      <c r="D28" s="43"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="53"/>
       <c r="E28" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="F28" s="42" t="s">
+      <c r="F28" s="52" t="s">
         <v>176</v>
       </c>
-      <c r="G28" s="43"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="45"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="92"/>
+      <c r="I28" s="93"/>
       <c r="Q28" s="2" t="s">
         <v>163</v>
       </c>
@@ -4788,21 +4784,21 @@
       </c>
     </row>
     <row r="29" spans="1:43">
-      <c r="A29" s="46"/>
+      <c r="A29" s="99"/>
       <c r="B29" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C29" s="42" t="s">
+      <c r="C29" s="52" t="s">
         <v>176</v>
       </c>
-      <c r="D29" s="43"/>
+      <c r="D29" s="53"/>
       <c r="E29" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="F29" s="42" t="s">
+      <c r="F29" s="52" t="s">
         <v>176</v>
       </c>
-      <c r="G29" s="43"/>
+      <c r="G29" s="53"/>
       <c r="H29" s="12" t="s">
         <v>178</v>
       </c>
@@ -4891,23 +4887,23 @@
       </c>
     </row>
     <row r="30" spans="1:43">
-      <c r="A30" s="46"/>
+      <c r="A30" s="99"/>
       <c r="B30" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="C30" s="42"/>
-      <c r="D30" s="43"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="53"/>
       <c r="E30" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="F30" s="42" t="s">
+      <c r="F30" s="52" t="s">
         <v>176</v>
       </c>
-      <c r="G30" s="43"/>
-      <c r="H30" s="44" t="s">
+      <c r="G30" s="53"/>
+      <c r="H30" s="92" t="s">
         <v>181</v>
       </c>
-      <c r="I30" s="45"/>
+      <c r="I30" s="93"/>
       <c r="Q30" s="2" t="s">
         <v>165</v>
       </c>
@@ -4992,61 +4988,61 @@
       </c>
     </row>
     <row r="31" spans="1:43">
-      <c r="A31" s="46"/>
+      <c r="A31" s="99"/>
       <c r="B31" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="C31" s="48" t="s">
+      <c r="C31" s="81" t="s">
         <v>176</v>
       </c>
-      <c r="D31" s="49"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="49"/>
+      <c r="D31" s="82"/>
+      <c r="E31" s="82"/>
+      <c r="F31" s="82"/>
       <c r="G31" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="H31" s="42"/>
-      <c r="I31" s="47"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="56"/>
       <c r="Q31" s="2" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:43">
-      <c r="A32" s="46"/>
+      <c r="A32" s="99"/>
       <c r="B32" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="C32" s="48" t="s">
+      <c r="C32" s="81" t="s">
         <v>185</v>
       </c>
-      <c r="D32" s="49"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="49"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="82"/>
+      <c r="F32" s="82"/>
       <c r="G32" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="H32" s="42" t="s">
+      <c r="H32" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="I32" s="47"/>
+      <c r="I32" s="56"/>
       <c r="Q32" s="2" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:43">
-      <c r="A33" s="46"/>
+      <c r="A33" s="99"/>
       <c r="B33" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="C33" s="50" t="s">
+      <c r="C33" s="86" t="s">
         <v>176</v>
       </c>
-      <c r="D33" s="51"/>
+      <c r="D33" s="87"/>
       <c r="E33" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="F33" s="52"/>
-      <c r="G33" s="53"/>
+      <c r="F33" s="100"/>
+      <c r="G33" s="101"/>
       <c r="H33" s="14" t="s">
         <v>189</v>
       </c>
@@ -5110,13 +5106,13 @@
       </c>
     </row>
     <row r="34" spans="1:43" ht="17.25" thickBot="1">
-      <c r="A34" s="46"/>
+      <c r="A34" s="99"/>
       <c r="B34" s="36" t="s">
         <v>190</v>
       </c>
-      <c r="C34" s="85"/>
-      <c r="D34" s="85"/>
-      <c r="E34" s="85"/>
+      <c r="C34" s="80"/>
+      <c r="D34" s="80"/>
+      <c r="E34" s="80"/>
       <c r="F34" s="37" t="s">
         <v>191</v>
       </c>
@@ -5290,14 +5286,14 @@
       </c>
     </row>
     <row r="36" spans="1:43">
-      <c r="B36" s="75" t="s">
+      <c r="B36" s="67" t="s">
         <v>139</v>
       </c>
-      <c r="C36" s="76"/>
-      <c r="D36" s="76"/>
-      <c r="E36" s="76"/>
-      <c r="F36" s="76"/>
-      <c r="G36" s="77"/>
+      <c r="C36" s="68"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="68"/>
+      <c r="F36" s="68"/>
+      <c r="G36" s="69"/>
       <c r="Q36" s="2" t="s">
         <v>145</v>
       </c>
@@ -5384,13 +5380,13 @@
       <c r="B37" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="C37" s="96" t="s">
+      <c r="C37" s="60" t="s">
         <v>231</v>
       </c>
-      <c r="D37" s="97"/>
-      <c r="E37" s="97"/>
-      <c r="F37" s="97"/>
-      <c r="G37" s="98"/>
+      <c r="D37" s="61"/>
+      <c r="E37" s="61"/>
+      <c r="F37" s="61"/>
+      <c r="G37" s="62"/>
       <c r="X37" s="2" t="s">
         <v>24</v>
       </c>
@@ -5474,13 +5470,13 @@
       <c r="B38" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="C38" s="96" t="s">
+      <c r="C38" s="60" t="s">
         <v>232</v>
       </c>
-      <c r="D38" s="97"/>
-      <c r="E38" s="97"/>
-      <c r="F38" s="97"/>
-      <c r="G38" s="98"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="61"/>
+      <c r="F38" s="61"/>
+      <c r="G38" s="62"/>
       <c r="X38" s="2" t="s">
         <v>26</v>
       </c>
@@ -5564,14 +5560,14 @@
       <c r="B39" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="C39" s="99" t="str">
+      <c r="C39" s="63" t="str">
         <f>C11</f>
         <v>陳耀晨</v>
       </c>
-      <c r="D39" s="100"/>
-      <c r="E39" s="100"/>
-      <c r="F39" s="100"/>
-      <c r="G39" s="101"/>
+      <c r="D39" s="64"/>
+      <c r="E39" s="64"/>
+      <c r="F39" s="64"/>
+      <c r="G39" s="65"/>
       <c r="Q39" s="2" t="s">
         <v>173</v>
       </c>
@@ -5655,87 +5651,87 @@
       </c>
     </row>
     <row r="40" spans="1:43" ht="17.25" thickBot="1">
-      <c r="C40" s="72"/>
-      <c r="D40" s="72"/>
-      <c r="E40" s="72"/>
-      <c r="F40" s="72"/>
-      <c r="G40" s="72"/>
+      <c r="C40" s="66"/>
+      <c r="D40" s="66"/>
+      <c r="E40" s="66"/>
+      <c r="F40" s="66"/>
+      <c r="G40" s="66"/>
       <c r="Q40" s="2" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:43">
-      <c r="B41" s="86" t="s">
+      <c r="B41" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="C41" s="87"/>
-      <c r="D41" s="87"/>
-      <c r="E41" s="87"/>
-      <c r="F41" s="87"/>
-      <c r="G41" s="88"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="44"/>
     </row>
     <row r="42" spans="1:43">
       <c r="B42" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="C42" s="70" t="s">
+      <c r="C42" s="79" t="s">
         <v>233</v>
       </c>
-      <c r="D42" s="71"/>
+      <c r="D42" s="77"/>
       <c r="E42" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="F42" s="71" t="s">
+      <c r="F42" s="77" t="s">
         <v>234</v>
       </c>
-      <c r="G42" s="84"/>
+      <c r="G42" s="78"/>
     </row>
     <row r="43" spans="1:43">
       <c r="B43" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="C43" s="71" t="s">
+      <c r="C43" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="71"/>
+      <c r="D43" s="77"/>
       <c r="E43" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="F43" s="71" t="s">
+      <c r="F43" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="G43" s="84"/>
+      <c r="G43" s="78"/>
     </row>
     <row r="44" spans="1:43" ht="17.25" thickBot="1">
       <c r="B44" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C44" s="79">
+      <c r="C44" s="71">
         <f xml:space="preserve"> VLOOKUP(F43,$Y$1:$AL$7,MATCH(C43,$Y$1:$AL$1,0),FALSE)</f>
         <v>6564</v>
       </c>
-      <c r="D44" s="79"/>
+      <c r="D44" s="71"/>
       <c r="E44" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F44" s="80">
+      <c r="F44" s="72">
         <f xml:space="preserve"> VLOOKUP(F43,$Y$10:$AL$16,MATCH(C43,$Y$10:$AL$10,0),FALSE)</f>
         <v>157536</v>
       </c>
-      <c r="G44" s="81"/>
+      <c r="G44" s="73"/>
     </row>
     <row r="45" spans="1:43" ht="17.25" thickBot="1">
       <c r="B45" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="78">
+      <c r="C45" s="70">
         <f>F44</f>
         <v>157536</v>
       </c>
-      <c r="D45" s="78"/>
-      <c r="E45" s="82"/>
-      <c r="F45" s="56"/>
-      <c r="G45" s="83"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="74"/>
+      <c r="F45" s="75"/>
+      <c r="G45" s="76"/>
     </row>
     <row r="47" spans="1:43">
       <c r="B47" s="5" t="s">
@@ -5795,6 +5791,56 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="z5QZqdGG19CI85gzb3YHj2+vVl4dWO/9L6Nh1clSYZeaRPt6GIUp547mUfphdfhIiKCo7gueR4ipCcsVudIjsQ==" saltValue="ANJ12Z4WoisMKg6+D2V2Ng==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="66">
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="A27:A34"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="B41:G41"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="C19:E19"/>
@@ -5811,56 +5857,6 @@
     <mergeCell ref="C37:G37"/>
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B27:I27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="A27:A34"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="F33:G33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="10">

--- a/申請書/和裕維力貸商品範本.xlsx
+++ b/申請書/和裕維力貸商品範本.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbf32e69ea87f61e/Desktop/claude/申請書/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbf32e69ea87f61e/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28715" documentId="13_ncr:1_{499913D0-2FE9-4655-B8BA-1A17E70F9329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FC2694E-E060-4583-9BC3-E0E432FCCE22}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{9B35BF75-B843-497F-8803-E0C9FE8395C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77436B0A-8471-457E-AA06-0C73798EB6C3}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="1995" windowWidth="17340" windowHeight="13485" xr2:uid="{99901B22-9634-4B91-9650-179AA17524FA}"/>
+    <workbookView xWindow="9615" yWindow="1455" windowWidth="23595" windowHeight="13485" xr2:uid="{99901B22-9634-4B91-9650-179AA17524FA}"/>
   </bookViews>
   <sheets>
     <sheet name="和裕維力貸" sheetId="7" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <definedName name="維力商品貸">和裕維力貸!$Q$44:$Q$46</definedName>
     <definedName name="維力機車貸">和裕維力貸!$R$44:$R$45</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -546,7 +546,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="225">
   <si>
     <t>期付款</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -934,6 +934,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>請選擇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>身份證發證地</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -998,6 +1002,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>萬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>聯絡人1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1123,7 +1131,14 @@
     <t>其它</t>
   </si>
   <si>
+    <t>知情</t>
+  </si>
+  <si>
     <t>銀行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1223,6 +1238,10 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
+    <t>萬</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
     <t>資金用途</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1231,6 +1250,10 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
+    <t>請選擇</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
     <t>照會時間</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -1243,14 +1266,14 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
+    <t>年  月</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>連帶保證人</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>超籍專使用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>963</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1275,120 +1298,49 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(U114/10版)</t>
+    <t>機車出廠年月</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(U115/05版)</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>家用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>保密</t>
+    <t>1.購買消費型產品</t>
+  </si>
+  <si>
+    <t>2.購買家電、家具</t>
+  </si>
+  <si>
+    <t>3.購買3C產品</t>
+  </si>
+  <si>
+    <t>4.房屋裝修</t>
+  </si>
+  <si>
+    <t>5.子女教育費</t>
+  </si>
+  <si>
+    <t>6.醫療保險費</t>
+  </si>
+  <si>
+    <t>7.出國旅遊</t>
+  </si>
+  <si>
+    <t>8.個人創業</t>
+  </si>
+  <si>
+    <t>請選擇</t>
   </si>
   <si>
     <t>維力商品專</t>
-  </si>
-  <si>
-    <t>友</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>陳耀晨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>H123407309</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>075/04/03</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>112/03/10換</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0953-119943</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>03-4026689</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>桃園市大溪區文化路103巷11號三樓</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>桃園市桃園區中山路1000之3號4樓之5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>宏羚公司</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工程師</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1年8月</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4萬4千</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>桃園市中壢區北園路12號</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>台灣大哥大</t>
-  </si>
-  <si>
-    <t>謝汶芮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>紀景淳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>夫妻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0976-276827</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0923-500672</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>台灣土地銀行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>平鎮分行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安卓手機</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OPPO A77</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1463,8 +1415,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Microsoft JhengHei"/>
+      <name val="標楷體"/>
       <family val="4"/>
       <charset val="136"/>
     </font>
@@ -1513,7 +1464,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -1956,12 +1907,86 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top/>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1973,7 +1998,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2061,10 +2086,6 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2099,101 +2120,216 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2205,119 +2341,31 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2635,7 +2683,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D59A2E1-63EA-4BE8-8C6C-E9F138B5D4F3}">
   <dimension ref="A1:AQ52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.5" style="2" customWidth="1"/>
     <col min="2" max="2" width="16.125" style="2" bestFit="1" customWidth="1"/>
@@ -2657,7 +2705,7 @@
     <col min="44" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:43" hidden="1">
+    <row r="1" spans="2:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="Q1" s="2" t="s">
         <v>46</v>
       </c>
@@ -2734,7 +2782,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="2:43" hidden="1">
+    <row r="2" spans="2:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="K2" s="6"/>
       <c r="Q2" s="2" t="s">
         <v>52</v>
@@ -2833,7 +2881,7 @@
         <v>35960</v>
       </c>
     </row>
-    <row r="3" spans="2:43" hidden="1">
+    <row r="3" spans="2:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="K3" s="6"/>
       <c r="Q3" s="2" t="s">
         <v>56</v>
@@ -2932,7 +2980,7 @@
         <v>24860</v>
       </c>
     </row>
-    <row r="4" spans="2:43" hidden="1">
+    <row r="4" spans="2:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="K4" s="6"/>
       <c r="R4" s="2" t="s">
         <v>60</v>
@@ -3028,7 +3076,7 @@
         <v>19260</v>
       </c>
     </row>
-    <row r="5" spans="2:43" hidden="1">
+    <row r="5" spans="2:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="K5" s="6"/>
       <c r="R5" s="2" t="s">
         <v>63</v>
@@ -3124,7 +3172,7 @@
         <v>15920</v>
       </c>
     </row>
-    <row r="6" spans="2:43" hidden="1">
+    <row r="6" spans="2:43" hidden="1" x14ac:dyDescent="0.25">
       <c r="K6" s="6"/>
       <c r="R6" s="2" t="s">
         <v>66</v>
@@ -3214,17 +3262,17 @@
         <v>13700</v>
       </c>
     </row>
-    <row r="7" spans="2:43" ht="26.25" thickBot="1">
-      <c r="B7" s="83" t="s">
-        <v>171</v>
-      </c>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
+    <row r="7" spans="2:43" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="77" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
       <c r="K7" s="6"/>
       <c r="R7" s="2" t="s">
         <v>68</v>
@@ -3311,23 +3359,23 @@
         <v>10940</v>
       </c>
     </row>
-    <row r="8" spans="2:43" ht="17.25" thickBot="1">
+    <row r="8" spans="2:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="84"/>
-      <c r="D8" s="85"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="79"/>
       <c r="E8" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="F8" s="84" t="s">
-        <v>210</v>
-      </c>
-      <c r="G8" s="85"/>
-      <c r="I8" s="41"/>
+        <v>179</v>
+      </c>
+      <c r="F8" s="78" t="s">
+        <v>224</v>
+      </c>
+      <c r="G8" s="79"/>
+      <c r="I8" s="10"/>
       <c r="J8" s="8"/>
       <c r="Q8" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>69</v>
@@ -3336,19 +3384,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:43" ht="17.25" thickBot="1">
+    <row r="9" spans="2:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
-      <c r="H9" s="75" t="s">
-        <v>207</v>
-      </c>
-      <c r="I9" s="75"/>
+      <c r="H9" s="69" t="s">
+        <v>214</v>
+      </c>
+      <c r="I9" s="69"/>
       <c r="Q9" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>70</v>
@@ -3357,20 +3405,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:43">
-      <c r="B10" s="45" t="s">
+    <row r="10" spans="2:43" x14ac:dyDescent="0.25">
+      <c r="B10" s="51" t="s">
         <v>110</v>
       </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="47"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="53"/>
       <c r="J10" s="10"/>
       <c r="Q10" s="2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="R10" s="2" t="s">
         <v>71</v>
@@ -3433,23 +3481,21 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="2:43">
+    <row r="11" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C11" s="79" t="s">
-        <v>212</v>
-      </c>
-      <c r="D11" s="77"/>
+      <c r="C11" s="73" t="s">
+        <v>173</v>
+      </c>
+      <c r="D11" s="73"/>
       <c r="E11" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="F11" s="77" t="s">
-        <v>213</v>
-      </c>
-      <c r="G11" s="77"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="95"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="86"/>
+      <c r="I11" s="87"/>
       <c r="J11" s="8"/>
       <c r="R11" s="2" t="s">
         <v>72</v>
@@ -3533,25 +3579,21 @@
         <v>215760</v>
       </c>
     </row>
-    <row r="12" spans="2:43">
+    <row r="12" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C12" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="D12" s="53"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="50"/>
       <c r="E12" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="F12" s="52" t="s">
-        <v>215</v>
-      </c>
-      <c r="G12" s="53"/>
-      <c r="H12" s="90" t="s">
-        <v>172</v>
-      </c>
-      <c r="I12" s="91"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="84" t="s">
+        <v>176</v>
+      </c>
+      <c r="I12" s="85"/>
       <c r="R12" s="2" t="s">
         <v>73</v>
       </c>
@@ -3634,25 +3676,25 @@
         <v>223740</v>
       </c>
     </row>
-    <row r="13" spans="2:43">
+    <row r="13" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B13" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="C13" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="53"/>
+      <c r="C13" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" s="50"/>
       <c r="E13" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="F13" s="49" t="s">
         <v>116</v>
       </c>
-      <c r="F13" s="52" t="s">
-        <v>68</v>
-      </c>
-      <c r="G13" s="53"/>
-      <c r="H13" s="92"/>
-      <c r="I13" s="93"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="76"/>
       <c r="Q13" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="R13" s="2" t="s">
         <v>74</v>
@@ -3736,27 +3778,25 @@
         <v>231120</v>
       </c>
     </row>
-    <row r="14" spans="2:43">
+    <row r="14" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="C14" s="52" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="53"/>
+        <v>118</v>
+      </c>
+      <c r="C14" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" s="50"/>
       <c r="E14" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="F14" s="52" t="s">
-        <v>216</v>
-      </c>
-      <c r="G14" s="53"/>
-      <c r="H14" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="I14" s="59"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="62" t="s">
+        <v>120</v>
+      </c>
+      <c r="I14" s="63"/>
       <c r="Q14" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="R14" s="2" t="s">
         <v>75</v>
@@ -3840,23 +3880,21 @@
         <v>238800</v>
       </c>
     </row>
-    <row r="15" spans="2:43">
+    <row r="15" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B15" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C15" s="81" t="s">
-        <v>218</v>
-      </c>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="89"/>
+        <v>121</v>
+      </c>
+      <c r="C15" s="47"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="83"/>
       <c r="G15" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="H15" s="52"/>
-      <c r="I15" s="56"/>
+        <v>122</v>
+      </c>
+      <c r="H15" s="49"/>
+      <c r="I15" s="60"/>
       <c r="Q15" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="R15" s="2" t="s">
         <v>76</v>
@@ -3940,25 +3978,25 @@
         <v>246600</v>
       </c>
     </row>
-    <row r="16" spans="2:43">
+    <row r="16" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B16" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="81" t="s">
-        <v>219</v>
-      </c>
-      <c r="D16" s="82"/>
-      <c r="E16" s="82"/>
-      <c r="F16" s="89"/>
+        <v>123</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="83"/>
       <c r="G16" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="H16" s="49" t="s">
         <v>124</v>
       </c>
-      <c r="H16" s="52" t="s">
-        <v>123</v>
-      </c>
-      <c r="I16" s="56"/>
+      <c r="I16" s="60"/>
       <c r="Q16" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R16" s="2" t="s">
         <v>77</v>
@@ -4042,29 +4080,25 @@
         <v>262560</v>
       </c>
     </row>
-    <row r="17" spans="1:43">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="C17" s="52" t="s">
-        <v>216</v>
-      </c>
-      <c r="D17" s="53"/>
+        <v>149</v>
+      </c>
+      <c r="C17" s="49"/>
+      <c r="D17" s="50"/>
       <c r="E17" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="F17" s="39" t="s">
-        <v>208</v>
+        <v>199</v>
+      </c>
+      <c r="F17" s="46" t="s">
+        <v>223</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="H17" s="52" t="s">
-        <v>217</v>
-      </c>
-      <c r="I17" s="56"/>
+        <v>126</v>
+      </c>
+      <c r="H17" s="49"/>
+      <c r="I17" s="60"/>
       <c r="Q17" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="R17" s="2" t="s">
         <v>78</v>
@@ -4073,29 +4107,25 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:43">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B18" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="C18" s="86" t="s">
-        <v>220</v>
-      </c>
-      <c r="D18" s="87"/>
-      <c r="E18" s="88"/>
+        <v>127</v>
+      </c>
+      <c r="C18" s="80"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="82"/>
       <c r="F18" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="G18" s="32" t="s">
-        <v>221</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="G18" s="31"/>
       <c r="H18" s="14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="R18" s="2" t="s">
         <v>79</v>
@@ -4104,29 +4134,27 @@
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:43">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B19" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C19" s="48" t="s">
-        <v>224</v>
-      </c>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
+        <v>130</v>
+      </c>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
       <c r="F19" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="G19" s="40" t="s">
-        <v>155</v>
+        <v>131</v>
+      </c>
+      <c r="G19" s="38" t="s">
+        <v>116</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="I19" s="29" t="s">
-        <v>223</v>
+        <v>132</v>
+      </c>
+      <c r="I19" s="28" t="s">
+        <v>133</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="R19" s="2" t="s">
         <v>80</v>
@@ -4135,31 +4163,31 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:43" ht="17.25" thickBot="1">
-      <c r="B20" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="C20" s="54" t="s">
-        <v>225</v>
-      </c>
-      <c r="D20" s="55"/>
-      <c r="E20" s="31" t="s">
-        <v>196</v>
-      </c>
-      <c r="F20" s="96"/>
-      <c r="G20" s="97"/>
-      <c r="H20" s="97"/>
-      <c r="I20" s="98"/>
+    <row r="20" spans="1:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="C20" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="D20" s="59"/>
+      <c r="E20" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="F20" s="88"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="89"/>
+      <c r="I20" s="90"/>
       <c r="Q20" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="R20" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:43" ht="17.25" thickBot="1">
+    <row r="21" spans="1:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="Q21" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="R21" s="2" t="s">
         <v>82</v>
@@ -4186,26 +4214,26 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:43">
-      <c r="B22" s="49" t="s">
-        <v>132</v>
-      </c>
-      <c r="C22" s="50"/>
+    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="B22" s="55" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22" s="56"/>
       <c r="D22" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E22" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="F22" s="50"/>
+        <v>146</v>
+      </c>
+      <c r="E22" s="57" t="s">
+        <v>135</v>
+      </c>
+      <c r="F22" s="56"/>
       <c r="G22" s="4" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="R22" s="2" t="s">
         <v>83</v>
@@ -4238,23 +4266,19 @@
         <v>547</v>
       </c>
     </row>
-    <row r="23" spans="1:43">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B23" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="C23" s="52" t="s">
-        <v>226</v>
-      </c>
-      <c r="D23" s="53"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="50"/>
       <c r="E23" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="F23" s="52" t="s">
-        <v>227</v>
-      </c>
-      <c r="G23" s="56"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="60"/>
       <c r="Q23" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="R23" s="2" t="s">
         <v>84</v>
@@ -4314,23 +4338,19 @@
         <v>103</v>
       </c>
     </row>
-    <row r="24" spans="1:43">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B24" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="C24" s="52" t="s">
-        <v>228</v>
-      </c>
-      <c r="D24" s="53"/>
+        <v>136</v>
+      </c>
+      <c r="C24" s="49"/>
+      <c r="D24" s="50"/>
       <c r="E24" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="F24" s="52" t="s">
-        <v>211</v>
-      </c>
-      <c r="G24" s="56"/>
+        <v>136</v>
+      </c>
+      <c r="F24" s="49"/>
+      <c r="G24" s="60"/>
       <c r="Q24" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="R24" s="2" t="s">
         <v>85</v>
@@ -4390,26 +4410,22 @@
         <v>108</v>
       </c>
     </row>
-    <row r="25" spans="1:43" ht="17.25" thickBot="1">
+    <row r="25" spans="1:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="C25" s="54" t="s">
-        <v>229</v>
-      </c>
-      <c r="D25" s="55"/>
+        <v>119</v>
+      </c>
+      <c r="C25" s="58"/>
+      <c r="D25" s="59"/>
       <c r="E25" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="F25" s="54" t="s">
-        <v>230</v>
-      </c>
-      <c r="G25" s="57"/>
+        <v>119</v>
+      </c>
+      <c r="F25" s="58"/>
+      <c r="G25" s="61"/>
       <c r="H25" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="R25" s="2" t="s">
         <v>86</v>
@@ -4494,9 +4510,9 @@
         <v>35960</v>
       </c>
     </row>
-    <row r="26" spans="1:43" ht="17.25" thickBot="1">
+    <row r="26" spans="1:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="Q26" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="R26" s="2" t="s">
         <v>87</v>
@@ -4581,22 +4597,20 @@
         <v>24860</v>
       </c>
     </row>
-    <row r="27" spans="1:43">
-      <c r="A27" s="99" t="s">
-        <v>200</v>
-      </c>
-      <c r="B27" s="45" t="s">
-        <v>199</v>
-      </c>
-      <c r="C27" s="46"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="47"/>
+    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A27" s="6"/>
+      <c r="B27" s="51" t="s">
+        <v>206</v>
+      </c>
+      <c r="C27" s="52"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="53"/>
       <c r="Q27" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="R27" s="2" t="s">
         <v>88</v>
@@ -4681,24 +4695,26 @@
         <v>19260</v>
       </c>
     </row>
-    <row r="28" spans="1:43">
-      <c r="A28" s="99"/>
+    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A28" s="6"/>
       <c r="B28" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C28" s="52"/>
-      <c r="D28" s="53"/>
+      <c r="C28" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="D28" s="50"/>
       <c r="E28" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="F28" s="52" t="s">
-        <v>176</v>
-      </c>
-      <c r="G28" s="53"/>
-      <c r="H28" s="92"/>
-      <c r="I28" s="93"/>
+      <c r="F28" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="G28" s="50"/>
+      <c r="H28" s="75"/>
+      <c r="I28" s="76"/>
       <c r="Q28" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="R28" s="2" t="s">
         <v>89</v>
@@ -4783,28 +4799,28 @@
         <v>15920</v>
       </c>
     </row>
-    <row r="29" spans="1:43">
-      <c r="A29" s="99"/>
+    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A29" s="6"/>
       <c r="B29" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C29" s="52" t="s">
-        <v>176</v>
-      </c>
-      <c r="D29" s="53"/>
+      <c r="C29" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="D29" s="50"/>
       <c r="E29" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="F29" s="52" t="s">
-        <v>176</v>
-      </c>
-      <c r="G29" s="53"/>
+        <v>181</v>
+      </c>
+      <c r="F29" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="G29" s="50"/>
       <c r="H29" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="I29" s="28"/>
+        <v>182</v>
+      </c>
+      <c r="I29" s="39"/>
       <c r="Q29" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="X29" s="2" t="s">
         <v>26</v>
@@ -4886,26 +4902,26 @@
         <v>13700</v>
       </c>
     </row>
-    <row r="30" spans="1:43">
-      <c r="A30" s="99"/>
+    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A30" s="6"/>
       <c r="B30" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="C30" s="52"/>
-      <c r="D30" s="53"/>
+        <v>183</v>
+      </c>
+      <c r="C30" s="49"/>
+      <c r="D30" s="50"/>
       <c r="E30" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="F30" s="49" t="s">
         <v>180</v>
       </c>
-      <c r="F30" s="52" t="s">
-        <v>176</v>
-      </c>
-      <c r="G30" s="53"/>
-      <c r="H30" s="92" t="s">
-        <v>181</v>
-      </c>
-      <c r="I30" s="93"/>
+      <c r="G30" s="50"/>
+      <c r="H30" s="75" t="s">
+        <v>185</v>
+      </c>
+      <c r="I30" s="76"/>
       <c r="Q30" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="X30" s="2" t="s">
         <v>29</v>
@@ -4987,68 +5003,68 @@
         <v>10940</v>
       </c>
     </row>
-    <row r="31" spans="1:43">
-      <c r="A31" s="99"/>
+    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A31" s="6"/>
       <c r="B31" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="C31" s="81" t="s">
-        <v>176</v>
-      </c>
-      <c r="D31" s="82"/>
-      <c r="E31" s="82"/>
-      <c r="F31" s="82"/>
+        <v>186</v>
+      </c>
+      <c r="C31" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="D31" s="48"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
       <c r="G31" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="H31" s="52"/>
-      <c r="I31" s="56"/>
+        <v>187</v>
+      </c>
+      <c r="H31" s="49"/>
+      <c r="I31" s="60"/>
       <c r="Q31" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
-    <row r="32" spans="1:43">
-      <c r="A32" s="99"/>
+    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
       <c r="B32" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="C32" s="81" t="s">
-        <v>185</v>
-      </c>
-      <c r="D32" s="82"/>
-      <c r="E32" s="82"/>
-      <c r="F32" s="82"/>
+        <v>188</v>
+      </c>
+      <c r="C32" s="47" t="s">
+        <v>189</v>
+      </c>
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
       <c r="G32" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="H32" s="52" t="s">
-        <v>198</v>
-      </c>
-      <c r="I32" s="56"/>
+        <v>190</v>
+      </c>
+      <c r="H32" s="49" t="s">
+        <v>204</v>
+      </c>
+      <c r="I32" s="60"/>
       <c r="Q32" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
-    <row r="33" spans="1:43">
-      <c r="A33" s="99"/>
+    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A33" s="6"/>
       <c r="B33" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="C33" s="86" t="s">
-        <v>176</v>
-      </c>
-      <c r="D33" s="87"/>
+        <v>191</v>
+      </c>
+      <c r="C33" s="80" t="s">
+        <v>180</v>
+      </c>
+      <c r="D33" s="81"/>
       <c r="E33" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="F33" s="100"/>
-      <c r="G33" s="101"/>
+        <v>192</v>
+      </c>
+      <c r="F33" s="96"/>
+      <c r="G33" s="97"/>
       <c r="H33" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I33" s="33"/>
+        <v>193</v>
+      </c>
+      <c r="I33" s="32"/>
       <c r="Q33" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Z33" s="2" t="s">
         <v>6</v>
@@ -5105,24 +5121,26 @@
         <v>103</v>
       </c>
     </row>
-    <row r="34" spans="1:43" ht="17.25" thickBot="1">
-      <c r="A34" s="99"/>
-      <c r="B34" s="36" t="s">
-        <v>190</v>
-      </c>
-      <c r="C34" s="80"/>
-      <c r="D34" s="80"/>
-      <c r="E34" s="80"/>
-      <c r="F34" s="37" t="s">
-        <v>191</v>
-      </c>
-      <c r="G34" s="34" t="s">
-        <v>192</v>
-      </c>
-      <c r="H34" s="38" t="s">
-        <v>193</v>
-      </c>
-      <c r="I34" s="35"/>
+    <row r="34" spans="1:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="6"/>
+      <c r="B34" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="C34" s="102"/>
+      <c r="D34" s="102"/>
+      <c r="E34" s="102"/>
+      <c r="F34" s="36" t="s">
+        <v>195</v>
+      </c>
+      <c r="G34" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="H34" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="I34" s="34" t="s">
+        <v>198</v>
+      </c>
       <c r="X34" s="2" t="s">
         <v>18</v>
       </c>
@@ -5202,9 +5220,9 @@
         <v>215760</v>
       </c>
     </row>
-    <row r="35" spans="1:43" ht="17.25" thickBot="1">
+    <row r="35" spans="1:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="Q35" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="X35" s="2" t="s">
         <v>20</v>
@@ -5285,17 +5303,17 @@
         <v>223740</v>
       </c>
     </row>
-    <row r="36" spans="1:43">
-      <c r="B36" s="67" t="s">
-        <v>139</v>
-      </c>
-      <c r="C36" s="68"/>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="69"/>
+    <row r="36" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="B36" s="99" t="s">
+        <v>141</v>
+      </c>
+      <c r="C36" s="100"/>
+      <c r="D36" s="100"/>
+      <c r="E36" s="100"/>
+      <c r="F36" s="100"/>
+      <c r="G36" s="101"/>
       <c r="Q36" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="X36" s="2" t="s">
         <v>22</v>
@@ -5376,17 +5394,15 @@
         <v>231120</v>
       </c>
     </row>
-    <row r="37" spans="1:43">
+    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B37" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="C37" s="60" t="s">
-        <v>231</v>
-      </c>
-      <c r="D37" s="61"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="61"/>
-      <c r="G37" s="62"/>
+        <v>172</v>
+      </c>
+      <c r="C37" s="103"/>
+      <c r="D37" s="104"/>
+      <c r="E37" s="104"/>
+      <c r="F37" s="104"/>
+      <c r="G37" s="105"/>
       <c r="X37" s="2" t="s">
         <v>24</v>
       </c>
@@ -5466,17 +5482,15 @@
         <v>238800</v>
       </c>
     </row>
-    <row r="38" spans="1:43">
+    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B38" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="C38" s="60" t="s">
-        <v>232</v>
-      </c>
-      <c r="D38" s="61"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="61"/>
-      <c r="G38" s="62"/>
+        <v>142</v>
+      </c>
+      <c r="C38" s="103"/>
+      <c r="D38" s="104"/>
+      <c r="E38" s="104"/>
+      <c r="F38" s="104"/>
+      <c r="G38" s="105"/>
       <c r="X38" s="2" t="s">
         <v>26</v>
       </c>
@@ -5556,20 +5570,20 @@
         <v>246600</v>
       </c>
     </row>
-    <row r="39" spans="1:43" ht="17.25" thickBot="1">
+    <row r="39" spans="1:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="C39" s="63" t="str">
+        <v>143</v>
+      </c>
+      <c r="C39" s="106" t="str">
         <f>C11</f>
-        <v>陳耀晨</v>
-      </c>
-      <c r="D39" s="64"/>
-      <c r="E39" s="64"/>
-      <c r="F39" s="64"/>
-      <c r="G39" s="65"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="D39" s="107"/>
+      <c r="E39" s="107"/>
+      <c r="F39" s="107"/>
+      <c r="G39" s="108"/>
       <c r="Q39" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="X39" s="2" t="s">
         <v>29</v>
@@ -5650,90 +5664,115 @@
         <v>262560</v>
       </c>
     </row>
-    <row r="40" spans="1:43" ht="17.25" thickBot="1">
-      <c r="C40" s="66"/>
-      <c r="D40" s="66"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="66"/>
-      <c r="G40" s="66"/>
+    <row r="40" spans="1:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="98"/>
+      <c r="D40" s="98"/>
+      <c r="E40" s="98"/>
+      <c r="F40" s="98"/>
+      <c r="G40" s="98"/>
       <c r="Q40" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="41" spans="1:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="93" t="s">
+        <v>137</v>
+      </c>
+      <c r="C41" s="94"/>
+      <c r="D41" s="94"/>
+      <c r="E41" s="94"/>
+      <c r="F41" s="94"/>
+      <c r="G41" s="94"/>
+      <c r="H41" s="94"/>
+      <c r="I41" s="95"/>
+    </row>
+    <row r="42" spans="1:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="41" t="s">
         <v>174</v>
       </c>
+      <c r="F42" s="71"/>
+      <c r="G42" s="72"/>
+      <c r="H42" s="91" t="s">
+        <v>213</v>
+      </c>
+      <c r="I42" s="92"/>
+      <c r="Q42" s="2" t="s">
+        <v>215</v>
+      </c>
     </row>
-    <row r="41" spans="1:43">
-      <c r="B41" s="42" t="s">
-        <v>135</v>
-      </c>
-      <c r="C41" s="43"/>
-      <c r="D41" s="43"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="44"/>
+    <row r="43" spans="1:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="C43" s="73" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="73"/>
+      <c r="E43" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="F43" s="73" t="s">
+        <v>20</v>
+      </c>
+      <c r="G43" s="74"/>
+      <c r="H43" s="78"/>
+      <c r="I43" s="79"/>
+      <c r="Q43" s="2" t="s">
+        <v>216</v>
+      </c>
     </row>
-    <row r="42" spans="1:43">
-      <c r="B42" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="C42" s="79" t="s">
-        <v>233</v>
-      </c>
-      <c r="D42" s="77"/>
-      <c r="E42" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="F42" s="77" t="s">
-        <v>234</v>
-      </c>
-      <c r="G42" s="78"/>
-    </row>
-    <row r="43" spans="1:43">
-      <c r="B43" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="C43" s="77" t="s">
-        <v>17</v>
-      </c>
-      <c r="D43" s="77"/>
-      <c r="E43" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="F43" s="77" t="s">
-        <v>29</v>
-      </c>
-      <c r="G43" s="78"/>
-    </row>
-    <row r="44" spans="1:43" ht="17.25" thickBot="1">
+    <row r="44" spans="1:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C44" s="71">
+      <c r="C44" s="65">
         <f xml:space="preserve"> VLOOKUP(F43,$Y$1:$AL$7,MATCH(C43,$Y$1:$AL$1,0),FALSE)</f>
-        <v>6564</v>
-      </c>
-      <c r="D44" s="71"/>
+        <v>3729</v>
+      </c>
+      <c r="D44" s="65"/>
       <c r="E44" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="F44" s="72">
+      <c r="F44" s="66">
         <f xml:space="preserve"> VLOOKUP(F43,$Y$10:$AL$16,MATCH(C43,$Y$10:$AL$10,0),FALSE)</f>
-        <v>157536</v>
-      </c>
-      <c r="G44" s="73"/>
+        <v>33561</v>
+      </c>
+      <c r="G44" s="67"/>
+      <c r="H44" s="42"/>
+      <c r="I44" s="43"/>
+      <c r="Q44" s="2" t="s">
+        <v>217</v>
+      </c>
     </row>
-    <row r="45" spans="1:43" ht="17.25" thickBot="1">
+    <row r="45" spans="1:43" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="70">
+      <c r="C45" s="64">
         <f>F44</f>
-        <v>157536</v>
-      </c>
-      <c r="D45" s="70"/>
-      <c r="E45" s="74"/>
-      <c r="F45" s="75"/>
-      <c r="G45" s="76"/>
+        <v>33561</v>
+      </c>
+      <c r="D45" s="64"/>
+      <c r="E45" s="68"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="44"/>
+      <c r="I45" s="45"/>
+      <c r="Q45" s="2" t="s">
+        <v>218</v>
+      </c>
     </row>
-    <row r="47" spans="1:43">
+    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="Q46" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B47" s="5" t="s">
         <v>2</v>
       </c>
@@ -5755,31 +5794,42 @@
       <c r="H47" s="5" t="s">
         <v>29</v>
       </c>
+      <c r="Q47" s="2" t="s">
+        <v>220</v>
+      </c>
     </row>
-    <row r="48" spans="1:43">
+    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B48" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>204</v>
+        <v>210</v>
+      </c>
+      <c r="Q48" s="2" t="s">
+        <v>221</v>
       </c>
     </row>
-    <row r="52" spans="2:8">
+    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q49" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="52" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B52" s="10"/>
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
@@ -5789,16 +5839,20 @@
       <c r="H52" s="10"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="z5QZqdGG19CI85gzb3YHj2+vVl4dWO/9L6Nh1clSYZeaRPt6GIUp547mUfphdfhIiKCo7gueR4ipCcsVudIjsQ==" saltValue="ANJ12Z4WoisMKg6+D2V2Ng==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
-  <mergeCells count="66">
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="A27:A34"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="C32:F32"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="aEn0LplLDp8rm/vzHgLNG4vxT//XxQfHYwJu4tlpFP7HCMQcRDDN4K+4sXeWIxWh2T5kfGTEPLxkZsJtIsTg9Q==" saltValue="Tkjoddg9zBzl2UZry3QmBA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <mergeCells count="67">
     <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="B41:I41"/>
+    <mergeCell ref="H43:I43"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="B27:I27"/>
@@ -5809,6 +5863,15 @@
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="F20:I20"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="C32:F32"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C17:D17"/>
@@ -5821,13 +5884,6 @@
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="H12:I12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="B36:G36"/>
     <mergeCell ref="C45:D45"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="F44:G44"/>
@@ -5836,12 +5892,10 @@
     <mergeCell ref="C42:D42"/>
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="F43:G43"/>
-    <mergeCell ref="C34:E34"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
     <mergeCell ref="C30:D30"/>
-    <mergeCell ref="B41:G41"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="B22:C22"/>
@@ -5854,12 +5908,9 @@
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="H17:I17"/>
     <mergeCell ref="H14:I14"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="10">
+  <dataValidations count="11">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C20:D20" xr:uid="{B58EF8D2-A61A-42AC-A8B9-4FB263078004}">
       <formula1>手機電信公司</formula1>
     </dataValidation>
@@ -5888,6 +5939,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:G8" xr:uid="{D6A111EE-89D2-4545-BCAE-F06C6D9556EF}">
       <formula1>分期項目</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F17" xr:uid="{B80582CF-0DAE-405A-B857-1382A8C3F442}">
+      <formula1>$Q$42:$Q$49</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
